--- a/aq_files/0095.xlsx
+++ b/aq_files/0095.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A dataset has long right tail. What type of skewness?</t>
-  </si>
-  <si>
-    <t>A dataset has long left tail. What type?</t>
-  </si>
-  <si>
-    <t>What does skewness measure?</t>
-  </si>
-  <si>
-    <t>What does kurtosis measure?</t>
-  </si>
-  <si>
-    <t>What is zero skewness?</t>
-  </si>
-  <si>
-    <t>A normal distribution has what kurtosis?</t>
-  </si>
-  <si>
-    <t>What is leptokurtic distribution?</t>
-  </si>
-  <si>
-    <t>What is platykurtic distribution?</t>
-  </si>
-  <si>
-    <t>High kurtosis indicates what?</t>
-  </si>
-  <si>
-    <t>Low kurtosis indicates what?</t>
-  </si>
-  <si>
-    <t>A dataset has extreme peaks. What kurtosis?</t>
-  </si>
-  <si>
-    <t>A dataset has flat shape. What kurtosis?</t>
-  </si>
-  <si>
-    <t>How does skewness affect mean?</t>
-  </si>
-  <si>
-    <t>What happens to median in skewed data?</t>
-  </si>
-  <si>
-    <t>A dataset has skewness = 0. What does it mean?</t>
-  </si>
-  <si>
-    <t>A dataset has kurtosis &gt; 3. What does it imply?</t>
-  </si>
-  <si>
-    <t>What is relationship between skewness and symmetry?</t>
-  </si>
-  <si>
-    <t>Why is kurtosis important?</t>
-  </si>
-  <si>
-    <t>A dataset has extreme outliers. Effect on kurtosis?</t>
-  </si>
-  <si>
-    <t>Why check skewness before modeling?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,968 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_ID,Product_Name,Category,Status,Return_Flag,Region_Code,Payment_Method,Shipping_Mode,Discount_Rate,Discount_Text,Sales_Amount,Quantity,Profit,Notes,Date_Recorded,Customer_Type,Priority,Size,Color,Rating</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,MacBook Pro,Electronics,Active,N,NW,Credit Card,Standard,0.05,5%,1299.99,1,389.99,Excellent customer,2024-01-05,Corporate,High,Large,Silver,5</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,Magic Mouse,Electronics,Active,N,NW,PayPal,Express,0.10,10%,79.99,3,23.99,,2024-01-05,Corporate,Medium,Small,White,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,Designer Jeans,Clothing,Active,N,SW,Debit Card,Standard,0.00,0%,89.99,2,26.99,First time customer,2024-01-06,Consumer,Medium,Medium,Blue,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,27-inch Monitor,Electronics,Active,N,SW,Credit Card,Express,0.15,15%,299.99,1,89.99,,2024-01-06,Consumer,High,Large,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,Executive Chair,Furniture,Active,N,NE,Credit Card,Standard,0.05,5%,399.99,2,119.99,VIP customer,2024-01-07,Corporate,High,Large,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,Mechanical Keyboard,Electronics,Delayed,N,NE,PayPal,Standard,0.10,10%,89.99,2,26.99,,2024-01-07,Consumer,Medium,Medium,RGB,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,Leather Jacket,Clothing,Active,N,WC,Debit Card,Express,0.20,20%,199.99,1,59.99,,2024-01-08,Home Office,High,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,iPad,Electronics,Active,N,WC,Credit Card,Standard,0.05,5%,499.99,1,149.99,,2024-01-08,Corporate,High,Medium,Space Gray,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,Floor Lamp,Furniture,Active,N,NW,PayPal,Standard,0.00,0%,79.99,2,23.99,,2024-01-09,Consumer,Low,Medium,Black,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,Running Shoes,Clothing,Returned,Y,NW,Debit Card,Express,0.10,10%,69.99,1,20.99,Size issue,2024-01-09,Consumer,Medium,Small,Blue,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,Gaming Laptop,Electronics,Active,N,SW,Credit Card,Standard,0.15,15%,1299.99,1,389.99,,2024-01-10,Corporate,High,Large,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,Headphones,Electronics,Active,N,NE,PayPal,Express,0.05,5%,149.99,2,44.99,,2024-01-10,Consumer,Medium,Medium,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,Wool Coat,Clothing,Active,N,WC,Debit Card,Standard,0.20,20%,189.99,1,56.99,,2024-01-11,Home Office,High,Large,Camel,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,Bookshelf,Furniture,Active,N,NW,Credit Card,Standard,0.10,10%,159.99,1,47.99,,2024-01-11,Corporate,Medium,Large,Oak,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,Smartphone,Electronics,Active,N,SW,Credit Card,Express,0.05,5%,699.99,2,209.99,,2024-01-12,Consumer,High,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,Dress Shirt,Clothing,Active,N,NE,PayPal,Standard,0.00,0%,59.99,3,17.99,,2024-01-12,Corporate,Medium,Medium,White,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,External SSD,Electronics,Active,N,WC,Debit Card,Standard,0.10,10%,99.99,1,29.99,,2024-01-13,Consumer,Low,Small,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,Hoodie,Clothing,Returned,Y,NW,PayPal,Express,0.05,5%,49.99,2,14.99,Wrong size,2024-01-13,Consumer,Medium,Medium,Gray,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,Gaming Desk,Furniture,Active,N,SW,Credit Card,Standard,0.15,15%,349.99,1,104.99,,2024-01-14,Corporate,High,Large,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,Webcam,Electronics,Active,N,NE,PayPal,Express,0.10,10%,79.99,2,23.99,,2024-01-14,Home Office,Medium,Small,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,Docking Station,Electronics,Active,N,WC,Debit Card,Standard,0.00,0%,129.99,1,38.99,,2024-02-01,Consumer,Medium,Medium,Silver,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,Winter Parka,Clothing,Active,N,NW,Credit Card,Standard,0.05,5%,179.99,1,53.99,,2024-02-01,Consumer,High,Large,Navy,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,Office Desk,Furniture,Active,N,SW,PayPal,Express,0.10,10%,449.99,1,134.99,,2024-02-02,Corporate,High,Large,Oak,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,USB-C Hub,Electronics,Active,N,NE,Debit Card,Standard,0.00,0%,39.99,3,11.99,,2024-02-02,Consumer,Low,Small,Silver,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,Casual Blazer,Clothing,Active,N,WC,Credit Card,Express,0.15,15%,149.99,1,44.99,,2024-02-03,Home Office,Medium,Medium,Navy,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,Gaming Mouse,Electronics,Returned,Y,NW,PayPal,Standard,0.10,10%,59.99,2,17.99,Defective product,2024-02-03,Consumer,Medium,Small,RGB,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,Laser Printer,Electronics,Active,N,SW,Debit Card,Standard,0.05,5%,199.99,1,59.99,,2024-02-04,Corporate,High,Large,White,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,Lounge Chair,Furniture,Active,N,NE,Credit Card,Standard,0.20,20%,279.99,1,83.99,,2024-02-04,Consumer,High,Large,Brown,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,Power Bank,Electronics,Active,N,WC,PayPal,Express,0.00,0%,49.99,4,14.99,,2024-02-05,Consumer,Low,Small,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,Wool Scarf,Clothing,Active,N,NW,Debit Card,Standard,0.10,10%,24.99,5,7.49,,2024-02-05,Consumer,Low,Small,Gray,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,Gaming Headset,Electronics,Active,N,SW,Credit Card,Express,0.05,5%,119.99,1,35.99,,2024-02-06,Corporate,Medium,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,Night Stand,Furniture,Active,N,NE,PayPal,Standard,0.10,10%,69.99,2,20.99,,2024-02-06,Home Office,Medium,Medium,Oak,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,Athletic Shoes,Clothing,Active,N,WC,Debit Card,Standard,0.15,15%,109.99,1,32.99,,2024-02-07,Consumer,Medium,Medium,Blue,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,Smart Watch,Electronics,Active,N,NW,Credit Card,Express,0.05,5%,199.99,1,59.99,,2024-02-07,Consumer,High,Small,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,Bluetooth Speaker,Electronics,Active,N,SW,PayPal,Standard,0.10,10%,79.99,2,23.99,,2024-02-08,Corporate,Medium,Small,Red,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,Cashmere Sweater,Clothing,Returned,Y,NE,Debit Card,Standard,0.00,0%,99.99,1,29.99,Quality issue,2024-02-08,Consumer,Medium,Medium,Cream,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,Bookshelf,Furniture,Active,N,WC,Credit Card,Express,0.05,5%,129.99,1,38.99,,2024-02-09,Home Office,Medium,Large,White,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,Mesh Router,Electronics,Active,N,NW,PayPal,Standard,0.10,10%,99.99,1,29.99,,2024-02-09,Consumer,Medium,Medium,White,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,Golf Polo,Clothing,Active,N,SW,Debit Card,Standard,0.15,15%,44.99,3,13.49,,2024-02-10,Consumer,Low,Medium,Blue,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,Graphics Card,Electronics,Active,N,WC,Credit Card,Express,0.20,20%,499.99,1,149.99,,2024-02-10,Corporate,High,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,Desktop PC,Electronics,Active,N,NW,PayPal,Standard,0.05,5%,999.99,1,299.99,,2024-03-01,Corporate,High,Large,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,Yoga Pants,Clothing,Active,N,SW,Debit Card,Express,0.00,0%,49.99,2,14.99,,2024-03-01,Consumer,Medium,Medium,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,Coffee Table,Furniture,Active,N,NE,Credit Card,Standard,0.10,10%,249.99,1,74.99,,2024-03-02,Corporate,High,Large,Oak,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,Smart Speaker,Electronics,Active,N,WC,PayPal,Express,0.00,0%,89.99,2,26.99,,2024-03-02,Home Office,Medium,Medium,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,Baseball Cap,Clothing,Active,N,NW,Debit Card,Standard,0.05,5%,19.99,4,5.99,,2024-03-03,Consumer,Low,Small,Navy,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,Quadcopter,Electronics,Active,N,SW,Credit Card,Express,0.10,10%,349.99,1,104.99,,2024-03-03,Consumer,High,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,Wall Mirror,Furniture,Active,N,NE,PayPal,Standard,0.00,0%,59.99,2,17.99,,2024-03-04,Consumer,Medium,Large,Silver,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,Flannel Shirt,Clothing,Active,N,WC,Debit Card,Standard,0.10,10%,49.99,2,14.99,,2024-03-04,Home Office,Medium,Medium,Red,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,Streaming Stick,Electronics,Returned,Y,NW,Credit Card,Standard,0.05,5%,29.99,3,8.99,Not working properly,2024-03-05,Consumer,Low,Small,Black,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,Leggings,Clothing,Active,N,SW,PayPal,Express,0.00,0%,29.99,4,8.99,,2024-03-05,Consumer,Medium,Small,Black,4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Replace all null/blank values in the 'Notes' column with 'No notes'. How many replacements were made?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'N' values in the 'Return_Flag' column with 'No' and 'Y' with 'Yes'.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Active' values in 'Status' column with 'Active Order' and 'Delayed' with 'Delayed Order' and 'Returned' with 'Returned Order'.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Replace all blank/null values in 'Rating' column with the average rating (4.2). How many blanks were replaced?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Corporate' values in 'Customer_Type' column with 'Business' and 'Consumer' with 'Individual' and 'Home Office' with 'Home'.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Black' colors in 'Color' column with 'Dark' and 'White' with 'Light'. How many replacements were made?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'High' priority values with 'High Priority' and 'Medium' with 'Standard Priority' and 'Low' with 'Low Priority'.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Large' size values with 'L' and 'Medium' with 'M' and 'Small' with 'S'.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Electronics' category values with 'Tech' and 'Clothing' with 'Apparel'.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Credit Card' payment methods with 'CC' and 'PayPal' with 'PP' and 'Debit Card' with 'DC'.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Standard' shipping mode with 'Std' and 'Express' with 'Exp'.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'NW' region codes with 'Northwest' and 'SW' with 'Southwest' and 'NE' with 'Northeast' and 'WC' with 'West Coast'.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Replace all discount values of 0.00 in 'Discount_Rate' column with 'No Discount' in a new text column.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Replace all '5' ratings in 'Rating' column with 'Excellent' and '4' with 'Good' and '3' with 'Average' and '2' with 'Poor'.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Replace all empty strings in 'Notes' column with 'No comments' and trim any leading/trailing spaces.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Replace all instances of 'Black' color with 'Dark' and also replace 'Gray' with 'Dark' to consolidate dark colors.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Replace all null values in 'Priority' column with 'Standard Priority' and in 'Size' column with 'Standard Size'.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'RGB' color values with 'Multi-Color' and 'Space Gray' with 'Gray' to standardize color naming.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Replace all text in 'Product_Name' column to proper case (first letter capital). Also replace any 'MacBook' with 'MacBook Pro' where applicable.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Unknown' or null values in 'Customer_Type' with 'Not Specified'. Also replace any blank values with 'Not Specified'.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>